--- a/data/por_departamento/Santa Ana/establecimientos_salud.xlsx
+++ b/data/por_departamento/Santa Ana/establecimientos_salud.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Establecimientos" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Establecimientos'!$A$1:$AA$72</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Establecimientos'!$A$1:$AA$69</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA72"/>
+  <dimension ref="A1:AA69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4489,7 +4489,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>geofabrik-way-6174168</t>
+          <t>geofabrik-way-7885242</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4499,12 +4499,12 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>way/6174168</t>
+          <t>way/7885242</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Hospital Nacional de Chalchuapa</t>
+          <t>Unidad de Salud</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -4534,7 +4534,7 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Chalchuapa</t>
+          <t>San Antonio Pajonal</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -4549,17 +4549,17 @@
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>7</t>
         </is>
       </c>
       <c r="V40" t="inlineStr">
         <is>
-          <t>13.98975638</t>
+          <t>14.19460667</t>
         </is>
       </c>
       <c r="W40" t="inlineStr">
         <is>
-          <t>-89.67814127</t>
+          <t>-89.58333448</t>
         </is>
       </c>
       <c r="X40" t="inlineStr">
@@ -4569,24 +4569,24 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>POLYGON ((-89.6793568 13.9891375, -89.6792877 13.9895088, -89.6791964 13.9898288, -89.6791741 13.9899057, -89.6791477 13.9899846, -89.6790948 13.9901385, -89.6790032 13.9903778, -89.6789664 13.990474, -89.6789217 13.9904661, -89.678877 13.9904582, -89.6787744 13.9904444, -89.6785805 13.9904146, -89.6784138 13.990387, -89.6783292 13.9903734, -89.6782885 13.9903665, -89.6782438 13.9903577, -89.6781859 13.9903409, -89.6781218 13.9903192, -89.6781063 13.9903132, -89.6779568 13.9902557, -89.6779399 13.9902492, -89.6778169 13.9902018, -89.6772997 13.9901512, -89.6764817 13.9901174, -89.6765281 13.9898455, -89.6764197 13.989817, -89.6765706 13.9895605, -89.6768608 13.9895983, -89.6769334 13.9896, -89.6771227 13.9895433, -89.6772466 13.9895262, -89.6773421 13.9895227, -89.677597 13.9895433, -89.6778793 13.9895398, -89.6778994 13.9893271, -89.6782158 13.989446, -89.678279 13.989082, -89.6782863 13.9890399, -89.6783023 13.9889395, -89.6786943 13.9889995, -89.679148 13.989069, -89.6793251 13.989098, -89.6793568 13.9891375))</t>
+          <t>POLYGON ((-89.5835932 14.1945667, -89.5835633 14.1946299, -89.5834778 14.1948109, -89.5830796 14.1946492, -89.5831511 14.1944837, -89.5831865 14.1944016, -89.5835932 14.1945667))</t>
         </is>
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/way/6174168</t>
+          <t>https://www.openstreetmap.org/way/7885242</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=13.98975638,-89.67814127</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=14.19460667,-89.58333448</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>geofabrik-way-7885242</t>
+          <t>geofabrik-way-398021070</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4596,12 +4596,12 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>way/7885242</t>
+          <t>way/398021070</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Unidad de Salud</t>
+          <t>Hospital San Antonio</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -4616,12 +4616,12 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Predio</t>
+          <t>Edificio</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>predio</t>
+          <t>edificio</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -4631,7 +4631,7 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>San Antonio Pajonal</t>
+          <t>Santa Ana</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -4651,12 +4651,12 @@
       </c>
       <c r="V41" t="inlineStr">
         <is>
-          <t>14.19460667</t>
+          <t>13.98289575</t>
         </is>
       </c>
       <c r="W41" t="inlineStr">
         <is>
-          <t>-89.58333448</t>
+          <t>-89.57434676</t>
         </is>
       </c>
       <c r="X41" t="inlineStr">
@@ -4666,24 +4666,24 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>POLYGON ((-89.5835932 14.1945667, -89.5835633 14.1946299, -89.5834778 14.1948109, -89.5830796 14.1946492, -89.5831511 14.1944837, -89.5831865 14.1944016, -89.5835932 14.1945667))</t>
+          <t>POLYGON ((-89.5745314 13.9829041, -89.5742195 13.9830267, -89.5741614 13.9828875, -89.5744733 13.982765, -89.5744827 13.982788, -89.5745177 13.9828662, -89.5745314 13.9829041))</t>
         </is>
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/way/7885242</t>
+          <t>https://www.openstreetmap.org/way/398021070</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=14.19460667,-89.58333448</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=13.98289575,-89.57434676</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>geofabrik-way-8013637</t>
+          <t>geofabrik-way-401503506</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4693,12 +4693,12 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>way/8013637</t>
+          <t>way/401503506</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Centro de Salud</t>
+          <t>Sin nombre</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -4713,12 +4713,12 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Predio</t>
+          <t>Edificio</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>predio</t>
+          <t>edificio</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -4728,7 +4728,7 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>Masahuat</t>
+          <t>Metapán</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -4743,17 +4743,17 @@
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="V42" t="inlineStr">
         <is>
-          <t>14.19151863</t>
+          <t>14.33150847</t>
         </is>
       </c>
       <c r="W42" t="inlineStr">
         <is>
-          <t>-89.42805966</t>
+          <t>-89.44693012</t>
         </is>
       </c>
       <c r="X42" t="inlineStr">
@@ -4763,39 +4763,39 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>POLYGON ((-89.4283373 14.1916773, -89.4281997 14.1916729, -89.4280206 14.1916671, -89.4278335 14.1916611, -89.427833 14.1915367, -89.4278322 14.191349, -89.4282322 14.1913631, -89.4283373 14.1916773))</t>
+          <t>POLYGON ((-89.4470115 14.3315375, -89.4468615 14.3315636, -89.4468559 14.3315333, -89.4468452 14.3315352, -89.4468374 14.3314933, -89.4469214 14.3314787, -89.4469179 14.3314597, -89.4469946 14.3314463, -89.4470115 14.3315375))</t>
         </is>
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/way/8013637</t>
+          <t>https://www.openstreetmap.org/way/401503506</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=14.19151863,-89.42805966</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=14.33150847,-89.44693012</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>geofabrik-way-398021070</t>
+          <t>hot-way-382586759</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>geofabrik</t>
+          <t>hot</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>way/398021070</t>
+          <t>way/382586759</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Hospital San Antonio</t>
+          <t>Hospital Regional ISSS Santa Ana</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Edificio</t>
+          <t>Polígono</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>edificio</t>
+          <t>poligono</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -4833,6 +4833,31 @@
           <t>Occidental</t>
         </is>
       </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>Santa Ana</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>Público</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Emergencia, Cirugía, Pediatría, Medicina interna, Ginecología, Psiquiatría, Oftalmología, Otorrinolaringología, Fisiatría</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>hospital</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>hospital</t>
+        </is>
+      </c>
       <c r="T43" t="inlineStr">
         <is>
           <t>Polygon</t>
@@ -4840,17 +4865,17 @@
       </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>17</t>
         </is>
       </c>
       <c r="V43" t="inlineStr">
         <is>
-          <t>13.98289575</t>
+          <t>13.97619791</t>
         </is>
       </c>
       <c r="W43" t="inlineStr">
         <is>
-          <t>-89.57434676</t>
+          <t>-89.56708345</t>
         </is>
       </c>
       <c r="X43" t="inlineStr">
@@ -4860,39 +4885,39 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>POLYGON ((-89.5745314 13.9829041, -89.5742195 13.9830267, -89.5741614 13.9828875, -89.5744733 13.982765, -89.5744827 13.982788, -89.5745177 13.9828662, -89.5745314 13.9829041))</t>
+          <t>POLYGON ((-89.5680845 13.9757447, -89.5676331 13.9755115, -89.5664684 13.9756954, -89.5663685 13.9760781, -89.5662724 13.97648, -89.5662577 13.9765448, -89.5667715 13.9771082, -89.5667801 13.9771153, -89.5667891 13.9771197, -89.5667984 13.9771198, -89.5668086 13.977117, -89.5668175 13.9771109, -89.5677609 13.9763307, -89.5677902 13.9763038, -89.5678072 13.9762829, -89.5678241 13.9762544, -89.5680845 13.9757447))</t>
         </is>
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/way/398021070</t>
+          <t>https://www.openstreetmap.org/way/382586759</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=13.98289575,-89.57434676</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=13.97619791,-89.56708345</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>geofabrik-way-401503506</t>
+          <t>hot-node-11316431152</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>geofabrik</t>
+          <t>hot</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>way/401503506</t>
+          <t>node/11316431152</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Sin nombre</t>
+          <t>Unidad de salud Santa Rosa Guachipilín</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -4907,12 +4932,12 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Edificio</t>
+          <t>Punto</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>edificio</t>
+          <t>punto</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -4930,66 +4955,81 @@
           <t>Occidental</t>
         </is>
       </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>Santa Rosa Guachipilín</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>Público</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Medicina general</t>
+        </is>
+      </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>Polygon</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="V44" t="inlineStr">
         <is>
-          <t>14.33150847</t>
+          <t>14.207747</t>
         </is>
       </c>
       <c r="W44" t="inlineStr">
         <is>
-          <t>-89.44693012</t>
+          <t>-89.3529914</t>
         </is>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>centroide_area</t>
+          <t>coordenada_original</t>
         </is>
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>POLYGON ((-89.4470115 14.3315375, -89.4468615 14.3315636, -89.4468559 14.3315333, -89.4468452 14.3315352, -89.4468374 14.3314933, -89.4469214 14.3314787, -89.4469179 14.3314597, -89.4469946 14.3314463, -89.4470115 14.3315375))</t>
+          <t>POINT (-89.3529914 14.207747)</t>
         </is>
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/way/401503506</t>
+          <t>https://www.openstreetmap.org/node/11316431152</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=14.33150847,-89.44693012</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=14.207747,-89.3529914</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>geofabrik-node-4072664247</t>
+          <t>hot-node-4363772912</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>geofabrik</t>
+          <t>hot</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>node/4072664247</t>
+          <t>node/4363772912</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Unidad de Salúd</t>
+          <t>Unidad de Salud</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -5019,7 +5059,7 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>San Sebastian Salitrillo</t>
+          <t>Metapán</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -5039,12 +5079,12 @@
       </c>
       <c r="V45" t="inlineStr">
         <is>
-          <t>13.9667512</t>
+          <t>14.2076344</t>
         </is>
       </c>
       <c r="W45" t="inlineStr">
         <is>
-          <t>-89.6343178</t>
+          <t>-89.3529889</t>
         </is>
       </c>
       <c r="X45" t="inlineStr">
@@ -5054,24 +5094,24 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>POINT (-89.6343178 13.9667512)</t>
+          <t>POINT (-89.3529889 14.2076344)</t>
         </is>
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/node/4072664247</t>
+          <t>https://www.openstreetmap.org/node/4363772912</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=13.9667512,-89.6343178</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=14.2076344,-89.3529889</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>hot-way-382586759</t>
+          <t>hot-node-9546640516</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -5081,32 +5121,32 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>way/382586759</t>
+          <t>node/9546640516</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Hospital Regional ISSS Santa Ana</t>
+          <t>Clínica Médica El Carmen</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Hospital</t>
+          <t>Clínica</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>hospital</t>
+          <t>clinica</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Polígono</t>
+          <t>Punto</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>poligono</t>
+          <t>punto</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -5129,71 +5169,51 @@
           <t>Santa Ana</t>
         </is>
       </c>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>Público</t>
-        </is>
-      </c>
-      <c r="P46" t="inlineStr">
-        <is>
-          <t>Emergencia, Cirugía, Pediatría, Medicina interna, Ginecología, Psiquiatría, Oftalmología, Otorrinolaringología, Fisiatría</t>
-        </is>
-      </c>
-      <c r="Q46" t="inlineStr">
-        <is>
-          <t>hospital</t>
-        </is>
-      </c>
-      <c r="R46" t="inlineStr">
-        <is>
-          <t>hospital</t>
-        </is>
-      </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>Polygon</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>1</t>
         </is>
       </c>
       <c r="V46" t="inlineStr">
         <is>
-          <t>13.97619791</t>
+          <t>13.9990121</t>
         </is>
       </c>
       <c r="W46" t="inlineStr">
         <is>
-          <t>-89.56708345</t>
+          <t>-89.551589</t>
         </is>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>centroide_area</t>
+          <t>coordenada_original</t>
         </is>
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>POLYGON ((-89.5680845 13.9757447, -89.5676331 13.9755115, -89.5664684 13.9756954, -89.5663685 13.9760781, -89.5662724 13.97648, -89.5662577 13.9765448, -89.5667715 13.9771082, -89.5667801 13.9771153, -89.5667891 13.9771197, -89.5667984 13.9771198, -89.5668086 13.977117, -89.5668175 13.9771109, -89.5677609 13.9763307, -89.5677902 13.9763038, -89.5678072 13.9762829, -89.5678241 13.9762544, -89.5680845 13.9757447))</t>
+          <t>POINT (-89.551589 13.9990121)</t>
         </is>
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/way/382586759</t>
+          <t>https://www.openstreetmap.org/node/9546640516</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=13.97619791,-89.56708345</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=13.9990121,-89.551589</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>hot-node-11316431152</t>
+          <t>hot-node-9546728317</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -5203,22 +5223,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>node/11316431152</t>
+          <t>node/9546728317</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Unidad de salud Santa Rosa Guachipilín</t>
+          <t>Clínica de Fisioterapia Mojica</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Hospital</t>
+          <t>Clínica</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>hospital</t>
+          <t>clinica</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -5238,7 +5258,7 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>Metapán</t>
+          <t>Santa Ana</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -5248,17 +5268,7 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>Santa Rosa Guachipilín</t>
-        </is>
-      </c>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>Público</t>
-        </is>
-      </c>
-      <c r="P47" t="inlineStr">
-        <is>
-          <t>Medicina general</t>
+          <t>Santa Ana</t>
         </is>
       </c>
       <c r="T47" t="inlineStr">
@@ -5273,12 +5283,12 @@
       </c>
       <c r="V47" t="inlineStr">
         <is>
-          <t>14.207747</t>
+          <t>13.9989879</t>
         </is>
       </c>
       <c r="W47" t="inlineStr">
         <is>
-          <t>-89.3529914</t>
+          <t>-89.5515953</t>
         </is>
       </c>
       <c r="X47" t="inlineStr">
@@ -5288,24 +5298,24 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>POINT (-89.3529914 14.207747)</t>
+          <t>POINT (-89.5515953 13.9989879)</t>
         </is>
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/node/11316431152</t>
+          <t>https://www.openstreetmap.org/node/9546728317</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=14.207747,-89.3529914</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=13.9989879,-89.5515953</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>hot-node-4363772912</t>
+          <t>hot-node-9546640512</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5315,22 +5325,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>node/4363772912</t>
+          <t>node/9546640512</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Unidad de Salud</t>
+          <t>Consultorio Médico Familiar Inmaculada María Auxiliadora</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Hospital</t>
+          <t>Clínica</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>hospital</t>
+          <t>clinica</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -5350,7 +5360,7 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>Metapán</t>
+          <t>Santa Ana</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -5358,6 +5368,16 @@
           <t>Occidental</t>
         </is>
       </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>Santa Ana</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Medicina general, Pediatría, Citología, Control prenatal</t>
+        </is>
+      </c>
       <c r="T48" t="inlineStr">
         <is>
           <t>Point</t>
@@ -5370,12 +5390,12 @@
       </c>
       <c r="V48" t="inlineStr">
         <is>
-          <t>14.2076344</t>
+          <t>13.9989165</t>
         </is>
       </c>
       <c r="W48" t="inlineStr">
         <is>
-          <t>-89.3529889</t>
+          <t>-89.5516122</t>
         </is>
       </c>
       <c r="X48" t="inlineStr">
@@ -5385,24 +5405,24 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>POINT (-89.3529889 14.2076344)</t>
+          <t>POINT (-89.5516122 13.9989165)</t>
         </is>
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/node/4363772912</t>
+          <t>https://www.openstreetmap.org/node/9546640512</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=14.2076344,-89.3529889</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=13.9989165,-89.5516122</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>hot-node-9546640516</t>
+          <t>hot-node-9546640503</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5412,12 +5432,12 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>node/9546640516</t>
+          <t>node/9546640503</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Clínica Médica El Carmen</t>
+          <t>Clínica Médica Costa</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -5455,11 +5475,6 @@
           <t>Occidental</t>
         </is>
       </c>
-      <c r="L49" t="inlineStr">
-        <is>
-          <t>Santa Ana</t>
-        </is>
-      </c>
       <c r="T49" t="inlineStr">
         <is>
           <t>Point</t>
@@ -5472,12 +5487,12 @@
       </c>
       <c r="V49" t="inlineStr">
         <is>
-          <t>13.9990121</t>
+          <t>13.9987736</t>
         </is>
       </c>
       <c r="W49" t="inlineStr">
         <is>
-          <t>-89.551589</t>
+          <t>-89.5516456</t>
         </is>
       </c>
       <c r="X49" t="inlineStr">
@@ -5487,24 +5502,24 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>POINT (-89.551589 13.9990121)</t>
+          <t>POINT (-89.5516456 13.9987736)</t>
         </is>
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/node/9546640516</t>
+          <t>https://www.openstreetmap.org/node/9546640503</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=13.9990121,-89.551589</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=13.9987736,-89.5516456</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>hot-node-9546728317</t>
+          <t>hot-node-4194539089</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5514,22 +5529,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>node/9546728317</t>
+          <t>node/4194539089</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Clínica de Fisioterapia Mojica</t>
+          <t>Cruz Roja Salvadoreña</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Clínica</t>
+          <t>Hospital</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>clinica</t>
+          <t>hospital</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -5574,12 +5589,12 @@
       </c>
       <c r="V50" t="inlineStr">
         <is>
-          <t>13.9989879</t>
+          <t>13.9929151</t>
         </is>
       </c>
       <c r="W50" t="inlineStr">
         <is>
-          <t>-89.5515953</t>
+          <t>-89.5565094</t>
         </is>
       </c>
       <c r="X50" t="inlineStr">
@@ -5589,24 +5604,24 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>POINT (-89.5515953 13.9989879)</t>
+          <t>POINT (-89.5565094 13.9929151)</t>
         </is>
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/node/9546728317</t>
+          <t>https://www.openstreetmap.org/node/4194539089</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=13.9989879,-89.5515953</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=13.9929151,-89.5565094</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>hot-node-9546640512</t>
+          <t>hot-node-9482314215</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5616,12 +5631,12 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>node/9546640512</t>
+          <t>node/9482314215</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Consultorio Médico Familiar Inmaculada María Auxiliadora</t>
+          <t>Médica Integral CIAMSA</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -5664,11 +5679,6 @@
           <t>Santa Ana</t>
         </is>
       </c>
-      <c r="P51" t="inlineStr">
-        <is>
-          <t>Medicina general, Pediatría, Citología, Control prenatal</t>
-        </is>
-      </c>
       <c r="T51" t="inlineStr">
         <is>
           <t>Point</t>
@@ -5681,12 +5691,12 @@
       </c>
       <c r="V51" t="inlineStr">
         <is>
-          <t>13.9989165</t>
+          <t>13.9914587</t>
         </is>
       </c>
       <c r="W51" t="inlineStr">
         <is>
-          <t>-89.5516122</t>
+          <t>-89.5526203</t>
         </is>
       </c>
       <c r="X51" t="inlineStr">
@@ -5696,24 +5706,24 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>POINT (-89.5516122 13.9989165)</t>
+          <t>POINT (-89.5526203 13.9914587)</t>
         </is>
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/node/9546640512</t>
+          <t>https://www.openstreetmap.org/node/9482314215</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=13.9989165,-89.5516122</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=13.9914587,-89.5526203</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>hot-node-9546640503</t>
+          <t>hot-node-9482314217</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5723,22 +5733,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>node/9546640503</t>
+          <t>node/9482314217</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Clínica Médica Costa</t>
+          <t>Hospital JABES</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Clínica</t>
+          <t>Hospital</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>clinica</t>
+          <t>hospital</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -5766,6 +5776,11 @@
           <t>Occidental</t>
         </is>
       </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>Santa Ana</t>
+        </is>
+      </c>
       <c r="T52" t="inlineStr">
         <is>
           <t>Point</t>
@@ -5778,12 +5793,12 @@
       </c>
       <c r="V52" t="inlineStr">
         <is>
-          <t>13.9987736</t>
+          <t>13.9911578</t>
         </is>
       </c>
       <c r="W52" t="inlineStr">
         <is>
-          <t>-89.5516456</t>
+          <t>-89.5522061</t>
         </is>
       </c>
       <c r="X52" t="inlineStr">
@@ -5793,24 +5808,24 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>POINT (-89.5516456 13.9987736)</t>
+          <t>POINT (-89.5522061 13.9911578)</t>
         </is>
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/node/9546640503</t>
+          <t>https://www.openstreetmap.org/node/9482314217</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=13.9987736,-89.5516456</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=13.9911578,-89.5522061</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>hot-node-4194539089</t>
+          <t>hot-node-4029002858</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5820,22 +5835,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>node/4194539089</t>
+          <t>node/4029002858</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Cruz Roja Salvadoreña</t>
+          <t>Clínica Médica</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Hospital</t>
+          <t>Clínica</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>hospital</t>
+          <t>clinica</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -5880,12 +5895,12 @@
       </c>
       <c r="V53" t="inlineStr">
         <is>
-          <t>13.9929151</t>
+          <t>13.9898839</t>
         </is>
       </c>
       <c r="W53" t="inlineStr">
         <is>
-          <t>-89.5565094</t>
+          <t>-89.5559835</t>
         </is>
       </c>
       <c r="X53" t="inlineStr">
@@ -5895,24 +5910,24 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>POINT (-89.5565094 13.9929151)</t>
+          <t>POINT (-89.5559835 13.9898839)</t>
         </is>
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/node/4194539089</t>
+          <t>https://www.openstreetmap.org/node/4029002858</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=13.9929151,-89.5565094</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=13.9898839,-89.5559835</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>hot-node-9482314215</t>
+          <t>hot-node-4039023143</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5922,12 +5937,12 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>node/9482314215</t>
+          <t>node/4039023143</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Médica Integral CIAMSA</t>
+          <t>Unidad de Salud</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -5965,9 +5980,9 @@
           <t>Occidental</t>
         </is>
       </c>
-      <c r="L54" t="inlineStr">
-        <is>
-          <t>Santa Ana</t>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>Público</t>
         </is>
       </c>
       <c r="T54" t="inlineStr">
@@ -5982,12 +5997,12 @@
       </c>
       <c r="V54" t="inlineStr">
         <is>
-          <t>13.9914587</t>
+          <t>13.9859691</t>
         </is>
       </c>
       <c r="W54" t="inlineStr">
         <is>
-          <t>-89.5526203</t>
+          <t>-89.5483079</t>
         </is>
       </c>
       <c r="X54" t="inlineStr">
@@ -5997,24 +6012,24 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>POINT (-89.5526203 13.9914587)</t>
+          <t>POINT (-89.5483079 13.9859691)</t>
         </is>
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/node/9482314215</t>
+          <t>https://www.openstreetmap.org/node/4039023143</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=13.9914587,-89.5526203</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=13.9859691,-89.5483079</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>hot-node-9482314217</t>
+          <t>hot-node-11603240722</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -6024,22 +6039,22 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>node/9482314217</t>
+          <t>node/11603240722</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Hospital JABES</t>
+          <t>Unidad Médica de Especialidades de Santa Ana UMES</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Hospital</t>
+          <t>Clínica</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>hospital</t>
+          <t>clinica</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -6067,11 +6082,6 @@
           <t>Occidental</t>
         </is>
       </c>
-      <c r="L55" t="inlineStr">
-        <is>
-          <t>Santa Ana</t>
-        </is>
-      </c>
       <c r="T55" t="inlineStr">
         <is>
           <t>Point</t>
@@ -6084,12 +6094,12 @@
       </c>
       <c r="V55" t="inlineStr">
         <is>
-          <t>13.9911578</t>
+          <t>13.9849966</t>
         </is>
       </c>
       <c r="W55" t="inlineStr">
         <is>
-          <t>-89.5522061</t>
+          <t>-89.5626963</t>
         </is>
       </c>
       <c r="X55" t="inlineStr">
@@ -6099,24 +6109,24 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>POINT (-89.5522061 13.9911578)</t>
+          <t>POINT (-89.5626963 13.9849966)</t>
         </is>
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/node/9482314217</t>
+          <t>https://www.openstreetmap.org/node/11603240722</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=13.9911578,-89.5522061</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=13.9849966,-89.5626963</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>hot-node-4029002858</t>
+          <t>hot-node-11301186990</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -6126,22 +6136,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>node/4029002858</t>
+          <t>node/11301186990</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Clínica Médica</t>
+          <t>UMES</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Clínica</t>
+          <t>Hospital</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>clinica</t>
+          <t>hospital</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -6174,6 +6184,16 @@
           <t>Santa Ana</t>
         </is>
       </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Cirugía, Gastroenterología, Homeopatía, Oncología, Ginecología</t>
+        </is>
+      </c>
       <c r="T56" t="inlineStr">
         <is>
           <t>Point</t>
@@ -6186,12 +6206,12 @@
       </c>
       <c r="V56" t="inlineStr">
         <is>
-          <t>13.9898839</t>
+          <t>13.9848983</t>
         </is>
       </c>
       <c r="W56" t="inlineStr">
         <is>
-          <t>-89.5559835</t>
+          <t>-89.5626976</t>
         </is>
       </c>
       <c r="X56" t="inlineStr">
@@ -6201,24 +6221,24 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>POINT (-89.5559835 13.9898839)</t>
+          <t>POINT (-89.5626976 13.9848983)</t>
         </is>
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/node/4029002858</t>
+          <t>https://www.openstreetmap.org/node/11301186990</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=13.9898839,-89.5559835</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=13.9848983,-89.5626976</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>hot-node-4039023143</t>
+          <t>hot-node-4457977504</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -6228,12 +6248,12 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>node/4039023143</t>
+          <t>node/4457977504</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Unidad de Salud</t>
+          <t>Clínica de Especialidades Médicas (CLEMED)</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -6271,11 +6291,6 @@
           <t>Occidental</t>
         </is>
       </c>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>Público</t>
-        </is>
-      </c>
       <c r="T57" t="inlineStr">
         <is>
           <t>Point</t>
@@ -6288,12 +6303,12 @@
       </c>
       <c r="V57" t="inlineStr">
         <is>
-          <t>13.9859691</t>
+          <t>13.9840406</t>
         </is>
       </c>
       <c r="W57" t="inlineStr">
         <is>
-          <t>-89.5483079</t>
+          <t>-89.5625357</t>
         </is>
       </c>
       <c r="X57" t="inlineStr">
@@ -6303,24 +6318,24 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>POINT (-89.5483079 13.9859691)</t>
+          <t>POINT (-89.5625357 13.9840406)</t>
         </is>
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/node/4039023143</t>
+          <t>https://www.openstreetmap.org/node/4457977504</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=13.9859691,-89.5483079</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=13.9840406,-89.5625357</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>hot-node-11603240722</t>
+          <t>hot-node-2072315429</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -6330,22 +6345,22 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>node/11603240722</t>
+          <t>node/2072315429</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Unidad Médica de Especialidades de Santa Ana UMES</t>
+          <t>Centro Médico</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Clínica</t>
+          <t>Hospital</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>clinica</t>
+          <t>hospital</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -6385,12 +6400,12 @@
       </c>
       <c r="V58" t="inlineStr">
         <is>
-          <t>13.9849966</t>
+          <t>13.9834149</t>
         </is>
       </c>
       <c r="W58" t="inlineStr">
         <is>
-          <t>-89.5626963</t>
+          <t>-89.5611765</t>
         </is>
       </c>
       <c r="X58" t="inlineStr">
@@ -6400,24 +6415,24 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>POINT (-89.5626963 13.9849966)</t>
+          <t>POINT (-89.5611765 13.9834149)</t>
         </is>
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/node/11603240722</t>
+          <t>https://www.openstreetmap.org/node/2072315429</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=13.9849966,-89.5626963</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=13.9834149,-89.5611765</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>hot-node-11301186990</t>
+          <t>hot-node-4015219631</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -6427,22 +6442,22 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>node/11301186990</t>
+          <t>node/4015219631</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>UMES</t>
+          <t>Unidad de Salud NATIVIDAD</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Hospital</t>
+          <t>Clínica</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>hospital</t>
+          <t>clinica</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -6470,19 +6485,14 @@
           <t>Occidental</t>
         </is>
       </c>
-      <c r="L59" t="inlineStr">
-        <is>
-          <t>Santa Ana</t>
-        </is>
-      </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>Privado</t>
+          <t>Público</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Cirugía, Gastroenterología, Homeopatía, Oncología, Ginecología</t>
+          <t>Odontología, Clínica, Medicina general</t>
         </is>
       </c>
       <c r="T59" t="inlineStr">
@@ -6497,12 +6507,12 @@
       </c>
       <c r="V59" t="inlineStr">
         <is>
-          <t>13.9848983</t>
+          <t>13.9832855</t>
         </is>
       </c>
       <c r="W59" t="inlineStr">
         <is>
-          <t>-89.5626976</t>
+          <t>-89.5370909</t>
         </is>
       </c>
       <c r="X59" t="inlineStr">
@@ -6512,24 +6522,24 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>POINT (-89.5626976 13.9848983)</t>
+          <t>POINT (-89.5370909 13.9832855)</t>
         </is>
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/node/11301186990</t>
+          <t>https://www.openstreetmap.org/node/4015219631</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=13.9848983,-89.5626976</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=13.9832855,-89.5370909</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>hot-node-4457977504</t>
+          <t>hot-node-4039077001</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -6539,12 +6549,12 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>node/4457977504</t>
+          <t>node/4039077001</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Clínica de Especialidades Médicas (CLEMED)</t>
+          <t>Unidad de Salud Barrio San Miguelito</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -6582,6 +6592,11 @@
           <t>Occidental</t>
         </is>
       </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>Público</t>
+        </is>
+      </c>
       <c r="T60" t="inlineStr">
         <is>
           <t>Point</t>
@@ -6594,12 +6609,12 @@
       </c>
       <c r="V60" t="inlineStr">
         <is>
-          <t>13.9840406</t>
+          <t>13.9820546</t>
         </is>
       </c>
       <c r="W60" t="inlineStr">
         <is>
-          <t>-89.5625357</t>
+          <t>-89.5527013</t>
         </is>
       </c>
       <c r="X60" t="inlineStr">
@@ -6609,24 +6624,24 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>POINT (-89.5625357 13.9840406)</t>
+          <t>POINT (-89.5527013 13.9820546)</t>
         </is>
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/node/4457977504</t>
+          <t>https://www.openstreetmap.org/node/4039077001</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=13.9840406,-89.5625357</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=13.9820546,-89.5527013</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>hot-node-2072315429</t>
+          <t>hot-node-14135035501</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6636,22 +6651,22 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>node/2072315429</t>
+          <t>node/14135035501</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Centro Médico</t>
+          <t>unidad de salud El palmar</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Hospital</t>
+          <t>Clínica</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>hospital</t>
+          <t>clinica</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -6691,12 +6706,12 @@
       </c>
       <c r="V61" t="inlineStr">
         <is>
-          <t>13.9834149</t>
+          <t>13.9802856</t>
         </is>
       </c>
       <c r="W61" t="inlineStr">
         <is>
-          <t>-89.5611765</t>
+          <t>-89.5736826</t>
         </is>
       </c>
       <c r="X61" t="inlineStr">
@@ -6706,24 +6721,24 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>POINT (-89.5611765 13.9834149)</t>
+          <t>POINT (-89.5736826 13.9802856)</t>
         </is>
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/node/2072315429</t>
+          <t>https://www.openstreetmap.org/node/14135035501</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=13.9834149,-89.5611765</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=13.9802856,-89.5736826</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>hot-node-4015219631</t>
+          <t>hot-node-8282371289</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6733,22 +6748,22 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>node/4015219631</t>
+          <t>node/8282371289</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Unidad de Salud NATIVIDAD</t>
+          <t>Clínica Médica M&amp;M</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Clínica</t>
+          <t>Otro</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>clinica</t>
+          <t>otro</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -6768,7 +6783,7 @@
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>Santa Ana</t>
+          <t>Coatepeque</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
@@ -6776,16 +6791,6 @@
           <t>Occidental</t>
         </is>
       </c>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>Público</t>
-        </is>
-      </c>
-      <c r="P62" t="inlineStr">
-        <is>
-          <t>Odontología, Clínica, Medicina general</t>
-        </is>
-      </c>
       <c r="T62" t="inlineStr">
         <is>
           <t>Point</t>
@@ -6798,12 +6803,12 @@
       </c>
       <c r="V62" t="inlineStr">
         <is>
-          <t>13.9832855</t>
+          <t>13.9079379</t>
         </is>
       </c>
       <c r="W62" t="inlineStr">
         <is>
-          <t>-89.5370909</t>
+          <t>-89.4926352</t>
         </is>
       </c>
       <c r="X62" t="inlineStr">
@@ -6813,24 +6818,24 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>POINT (-89.5370909 13.9832855)</t>
+          <t>POINT (-89.4926352 13.9079379)</t>
         </is>
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/node/4015219631</t>
+          <t>https://www.openstreetmap.org/node/8282371289</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=13.9832855,-89.5370909</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=13.9079379,-89.4926352</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>hot-node-4039077001</t>
+          <t>hot-node-5368595423</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6840,22 +6845,22 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>node/4039077001</t>
+          <t>node/5368595423</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Unidad de Salud Barrio San Miguelito</t>
+          <t>Comandos de Salvamento de Ciudad Arce</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Clínica</t>
+          <t>Consultorio</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>clinica</t>
+          <t>consultorio</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -6875,7 +6880,7 @@
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>Santa Ana</t>
+          <t>Coatepeque</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
@@ -6883,11 +6888,6 @@
           <t>Occidental</t>
         </is>
       </c>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>Público</t>
-        </is>
-      </c>
       <c r="T63" t="inlineStr">
         <is>
           <t>Point</t>
@@ -6900,12 +6900,12 @@
       </c>
       <c r="V63" t="inlineStr">
         <is>
-          <t>13.9820546</t>
+          <t>13.8423474</t>
         </is>
       </c>
       <c r="W63" t="inlineStr">
         <is>
-          <t>-89.5527013</t>
+          <t>-89.4458648</t>
         </is>
       </c>
       <c r="X63" t="inlineStr">
@@ -6915,24 +6915,24 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>POINT (-89.5527013 13.9820546)</t>
+          <t>POINT (-89.4458648 13.8423474)</t>
         </is>
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/node/4039077001</t>
+          <t>https://www.openstreetmap.org/node/5368595423</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=13.9820546,-89.5527013</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=13.8423474,-89.4458648</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>hot-node-14135035501</t>
+          <t>hot-node-4072664247</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6942,22 +6942,22 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>node/14135035501</t>
+          <t>node/4072664247</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>unidad de salud El palmar</t>
+          <t>Unidad de Salúd</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Clínica</t>
+          <t>Hospital</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>clinica</t>
+          <t>hospital</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -6977,7 +6977,7 @@
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>Santa Ana</t>
+          <t>Chalchuapa</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
@@ -6985,6 +6985,11 @@
           <t>Occidental</t>
         </is>
       </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>San Sebastian Salitrillo</t>
+        </is>
+      </c>
       <c r="T64" t="inlineStr">
         <is>
           <t>Point</t>
@@ -6997,12 +7002,12 @@
       </c>
       <c r="V64" t="inlineStr">
         <is>
-          <t>13.9802856</t>
+          <t>13.9667512</t>
         </is>
       </c>
       <c r="W64" t="inlineStr">
         <is>
-          <t>-89.5736826</t>
+          <t>-89.6343178</t>
         </is>
       </c>
       <c r="X64" t="inlineStr">
@@ -7012,24 +7017,24 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>POINT (-89.5736826 13.9802856)</t>
+          <t>POINT (-89.6343178 13.9667512)</t>
         </is>
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/node/14135035501</t>
+          <t>https://www.openstreetmap.org/node/4072664247</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=13.9802856,-89.5736826</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=13.9667512,-89.6343178</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>hot-node-8282371289</t>
+          <t>hot-node-11603325086</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -7039,22 +7044,22 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>node/8282371289</t>
+          <t>node/11603325086</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Clínica Médica M&amp;M</t>
+          <t>Unidad Médica Especializada Umes Chalcuapa</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Clínica</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>otro</t>
+          <t>clinica</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -7074,7 +7079,7 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>Coatepeque</t>
+          <t>Chalchuapa</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
@@ -7082,6 +7087,11 @@
           <t>Occidental</t>
         </is>
       </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>Santa Ana</t>
+        </is>
+      </c>
       <c r="T65" t="inlineStr">
         <is>
           <t>Point</t>
@@ -7094,12 +7104,12 @@
       </c>
       <c r="V65" t="inlineStr">
         <is>
-          <t>13.9079379</t>
+          <t>13.9827828</t>
         </is>
       </c>
       <c r="W65" t="inlineStr">
         <is>
-          <t>-89.4926352</t>
+          <t>-89.6742672</t>
         </is>
       </c>
       <c r="X65" t="inlineStr">
@@ -7109,24 +7119,24 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>POINT (-89.4926352 13.9079379)</t>
+          <t>POINT (-89.6742672 13.9827828)</t>
         </is>
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/node/8282371289</t>
+          <t>https://www.openstreetmap.org/node/11603325086</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=13.9079379,-89.4926352</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=13.9827828,-89.6742672</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>hot-node-5368595423</t>
+          <t>hot-node-3814809441</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -7136,22 +7146,22 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>node/5368595423</t>
+          <t>node/3814809441</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Comandos de Salvamento de Ciudad Arce</t>
+          <t>Clínica Orden de Malta</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Consultorio</t>
+          <t>Clínica</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>consultorio</t>
+          <t>clinica</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -7171,7 +7181,7 @@
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>Coatepeque</t>
+          <t>Chalchuapa</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
@@ -7191,12 +7201,12 @@
       </c>
       <c r="V66" t="inlineStr">
         <is>
-          <t>13.8423474</t>
+          <t>13.9870837</t>
         </is>
       </c>
       <c r="W66" t="inlineStr">
         <is>
-          <t>-89.4458648</t>
+          <t>-89.6855623</t>
         </is>
       </c>
       <c r="X66" t="inlineStr">
@@ -7206,24 +7216,24 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>POINT (-89.4458648 13.8423474)</t>
+          <t>POINT (-89.6855623 13.9870837)</t>
         </is>
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/node/5368595423</t>
+          <t>https://www.openstreetmap.org/node/3814809441</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=13.8423474,-89.4458648</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=13.9870837,-89.6855623</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>hot-node-4072664247</t>
+          <t>hot-node-4039099453</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -7233,22 +7243,22 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>node/4072664247</t>
+          <t>node/4039099453</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Unidad de Salúd</t>
+          <t>Clínica Pediátrica</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Hospital</t>
+          <t>Clínica</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>hospital</t>
+          <t>clinica</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -7268,7 +7278,7 @@
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>Chalchuapa</t>
+          <t>Metapán</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
@@ -7278,7 +7288,7 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>San Sebastian Salitrillo</t>
+          <t>Metapán</t>
         </is>
       </c>
       <c r="T67" t="inlineStr">
@@ -7293,12 +7303,12 @@
       </c>
       <c r="V67" t="inlineStr">
         <is>
-          <t>13.9667512</t>
+          <t>14.330812</t>
         </is>
       </c>
       <c r="W67" t="inlineStr">
         <is>
-          <t>-89.6343178</t>
+          <t>-89.4432206</t>
         </is>
       </c>
       <c r="X67" t="inlineStr">
@@ -7308,24 +7318,24 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>POINT (-89.6343178 13.9667512)</t>
+          <t>POINT (-89.4432206 14.330812)</t>
         </is>
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/node/4072664247</t>
+          <t>https://www.openstreetmap.org/node/4039099453</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=13.9667512,-89.6343178</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=14.330812,-89.4432206</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>hot-node-11603325086</t>
+          <t>hot-node-4039271194</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -7335,12 +7345,12 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>node/11603325086</t>
+          <t>node/4039271194</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Unidad Médica Especializada Umes Chalcuapa</t>
+          <t>Ultrasonografia</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -7370,7 +7380,7 @@
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>Chalchuapa</t>
+          <t>Metapán</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
@@ -7380,7 +7390,7 @@
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>Santa Ana</t>
+          <t>Metapán</t>
         </is>
       </c>
       <c r="T68" t="inlineStr">
@@ -7395,12 +7405,12 @@
       </c>
       <c r="V68" t="inlineStr">
         <is>
-          <t>13.9827828</t>
+          <t>14.3306656</t>
         </is>
       </c>
       <c r="W68" t="inlineStr">
         <is>
-          <t>-89.6742672</t>
+          <t>-89.4430848</t>
         </is>
       </c>
       <c r="X68" t="inlineStr">
@@ -7410,24 +7420,24 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>POINT (-89.6742672 13.9827828)</t>
+          <t>POINT (-89.4430848 14.3306656)</t>
         </is>
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/node/11603325086</t>
+          <t>https://www.openstreetmap.org/node/4039271194</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=13.9827828,-89.6742672</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=14.3306656,-89.4430848</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>hot-node-3814809441</t>
+          <t>hot-node-4247184793</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -7437,12 +7447,12 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>node/3814809441</t>
+          <t>node/4247184793</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Clínica Orden de Malta</t>
+          <t>Clínica ISBM Metapán</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -7472,7 +7482,7 @@
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>Chalchuapa</t>
+          <t>Metapán</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
@@ -7492,12 +7502,12 @@
       </c>
       <c r="V69" t="inlineStr">
         <is>
-          <t>13.9870837</t>
+          <t>14.32657</t>
         </is>
       </c>
       <c r="W69" t="inlineStr">
         <is>
-          <t>-89.6855623</t>
+          <t>-89.4443733</t>
         </is>
       </c>
       <c r="X69" t="inlineStr">
@@ -7507,323 +7517,22 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>POINT (-89.6855623 13.9870837)</t>
+          <t>POINT (-89.4443733 14.32657)</t>
         </is>
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/node/3814809441</t>
+          <t>https://www.openstreetmap.org/node/4247184793</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
-        <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=13.9870837,-89.6855623</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>hot-node-4039099453</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>hot</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>node/4039099453</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>Clínica Pediátrica</t>
-        </is>
-      </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>Clínica</t>
-        </is>
-      </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>clinica</t>
-        </is>
-      </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>Punto</t>
-        </is>
-      </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>punto</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>Santa Ana</t>
-        </is>
-      </c>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t>Metapán</t>
-        </is>
-      </c>
-      <c r="K70" t="inlineStr">
-        <is>
-          <t>Occidental</t>
-        </is>
-      </c>
-      <c r="L70" t="inlineStr">
-        <is>
-          <t>Metapán</t>
-        </is>
-      </c>
-      <c r="T70" t="inlineStr">
-        <is>
-          <t>Point</t>
-        </is>
-      </c>
-      <c r="U70" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="V70" t="inlineStr">
-        <is>
-          <t>14.330812</t>
-        </is>
-      </c>
-      <c r="W70" t="inlineStr">
-        <is>
-          <t>-89.4432206</t>
-        </is>
-      </c>
-      <c r="X70" t="inlineStr">
-        <is>
-          <t>coordenada_original</t>
-        </is>
-      </c>
-      <c r="Y70" t="inlineStr">
-        <is>
-          <t>POINT (-89.4432206 14.330812)</t>
-        </is>
-      </c>
-      <c r="Z70" t="inlineStr">
-        <is>
-          <t>https://www.openstreetmap.org/node/4039099453</t>
-        </is>
-      </c>
-      <c r="AA70" t="inlineStr">
-        <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=14.330812,-89.4432206</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>hot-node-4039271194</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>hot</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>node/4039271194</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>Ultrasonografia</t>
-        </is>
-      </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>Clínica</t>
-        </is>
-      </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>clinica</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>Punto</t>
-        </is>
-      </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>punto</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>Santa Ana</t>
-        </is>
-      </c>
-      <c r="J71" t="inlineStr">
-        <is>
-          <t>Metapán</t>
-        </is>
-      </c>
-      <c r="K71" t="inlineStr">
-        <is>
-          <t>Occidental</t>
-        </is>
-      </c>
-      <c r="L71" t="inlineStr">
-        <is>
-          <t>Metapán</t>
-        </is>
-      </c>
-      <c r="T71" t="inlineStr">
-        <is>
-          <t>Point</t>
-        </is>
-      </c>
-      <c r="U71" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="V71" t="inlineStr">
-        <is>
-          <t>14.3306656</t>
-        </is>
-      </c>
-      <c r="W71" t="inlineStr">
-        <is>
-          <t>-89.4430848</t>
-        </is>
-      </c>
-      <c r="X71" t="inlineStr">
-        <is>
-          <t>coordenada_original</t>
-        </is>
-      </c>
-      <c r="Y71" t="inlineStr">
-        <is>
-          <t>POINT (-89.4430848 14.3306656)</t>
-        </is>
-      </c>
-      <c r="Z71" t="inlineStr">
-        <is>
-          <t>https://www.openstreetmap.org/node/4039271194</t>
-        </is>
-      </c>
-      <c r="AA71" t="inlineStr">
-        <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=14.3306656,-89.4430848</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>hot-node-4247184793</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>hot</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>node/4247184793</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>Clínica ISBM Metapán</t>
-        </is>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>Clínica</t>
-        </is>
-      </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>clinica</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>Punto</t>
-        </is>
-      </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>punto</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>Santa Ana</t>
-        </is>
-      </c>
-      <c r="J72" t="inlineStr">
-        <is>
-          <t>Metapán</t>
-        </is>
-      </c>
-      <c r="K72" t="inlineStr">
-        <is>
-          <t>Occidental</t>
-        </is>
-      </c>
-      <c r="T72" t="inlineStr">
-        <is>
-          <t>Point</t>
-        </is>
-      </c>
-      <c r="U72" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="V72" t="inlineStr">
-        <is>
-          <t>14.32657</t>
-        </is>
-      </c>
-      <c r="W72" t="inlineStr">
-        <is>
-          <t>-89.4443733</t>
-        </is>
-      </c>
-      <c r="X72" t="inlineStr">
-        <is>
-          <t>coordenada_original</t>
-        </is>
-      </c>
-      <c r="Y72" t="inlineStr">
-        <is>
-          <t>POINT (-89.4443733 14.32657)</t>
-        </is>
-      </c>
-      <c r="Z72" t="inlineStr">
-        <is>
-          <t>https://www.openstreetmap.org/node/4247184793</t>
-        </is>
-      </c>
-      <c r="AA72" t="inlineStr">
         <is>
           <t>https://www.google.com/maps/search/?api=1&amp;query=14.32657,-89.4443733</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AA72"/>
+  <autoFilter ref="A1:AA69"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>